--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5572,6 +5572,33 @@
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>BUILD 52 CUT (v1.1.0 build 52 — number read OFF the finished build, from commit ec8e487 on taxonomy-v1.0.7, PUSHED before the cut so it is reproducible from the remote) after the founder's explicit "cut the build" to a presented pre-build checklist. Gate satisfied in order: scope complete (59/59 tracker rows; 13 commits since build 51, all from the founder's same-day device findings), audits FINISHED (open-gaps ledger 9 of 9 closed), adversarial journey pass green (5 suites / 64 tests), then the checklist. Fresh gates at the cut: 1,522 tests green, tsc clean, UI-test gate passing, clean tree. Contents: the account-naming rule, square banners app-wide, one money size and the 8-point right-edge fix, a Sync-now that syncs, a dead connection that says so, cash-means-cash enforced where data arrives, the leftover-is-cash rule, deposits landing in cash, income no longer guessed onto holdings, activity newest-first, the retirement card speaking below 80%, measured volatility, sample-and-ask, and the rewritten odds info dot. Walk sheet: docs/FCC-core-55-70/build52-founder-walk-2026-08-11.xlsx (26 rows, organised by the founder's own findings).</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "cut the build" (2026-08-11), replying to the pre-build checklist.</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5599,6 +5599,33 @@
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (fix-it sheet) — the sync told the truth about nothing</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>THREE FIXES BEHIND ONE FOUNDER REPORT. (a) THE MESSAGE LIED BY OMISSION: the sheet ignored what the sync returned and always said "Updated", so when nothing was refreshed it claimed success while both rows sat exactly where they were. It now reports the actual count — "Updated 2 accounts" — or, at zero, "Nothing could be refreshed — your broker didn't answer. That usually means the connection has expired: use Reconnect below." (b) THERE WAS NOWHERE TO RE-LOGIN: the sheet told people a re-login was needed while offering only a Sync button. Every connection row now carries a second door, Reconnect, exactly as the approved State F mock drew it ("Sync now › Reconnect ›") — a sync can never revive a connection the provider has dropped. (c) THE ROOT CAUSE OF THE SILENCE: when the provider reports NO connections while the app still holds accounts marked connected (a revoked link, an expired session, or a provider-side user reset — the founder ran a SnapTrade purge on 2026-08-04), nothing threw, so nothing was recorded and those accounts just aged quietly. Every such account is now recorded as unreachable, so it SAYS it cannot be refreshed and offers the re-login.</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Founder device finding 2026-08-11: "pressed sync now... the message says Updated. Anything still listed here needs a re-login. Not sure what got updated, both accounts still listed to sync. Also no place to re-login."</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5626,6 +5626,33 @@
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Plan — the three questions (NEW screen)</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>A LINE THAT NAMES AN ANSWER NOW LANDS ON THAT ANSWER. "Add your age and it becomes yours" went to the Plan HUB, whose own "1 answer left" went to Sharpen your plan — a SEVEN-item completeness checklist driven by a different engine than the three-answer count. Three hops to answer one question, and the last one did not ask it. Worse, the app had NO screen that captured your age at all: the only writer was the What-if slider, which is why the line had nowhere sensible to go. NEW /plan-answers asks exactly the answers the odds are missing (your age · what you spend · what you have), each saving as you type, with ?focus= opening straight at one; it shows THE ODDS on the same screen the moment all three are in, so nobody has to travel to find out whether it worked. Net worth's sample line and the Plan hub's door both point here now. Sharpen keeps its own job — how complete is the whole plan — and stops being the destination for "see your real odds", which is a different question. The three ways in (connect · import · by hand) moved to ONE shared list so two screens cannot word them differently. Route whitelisted in the guard (the T22 class), and the dead-route guard covers it.</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Founder finding 2026-08-11: "when I click add your age it takes me to plan main screen, and 1 answer left takes me to sharpen your plan. Does not seem like optimal flow."</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5653,6 +5653,60 @@
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Retirement — what counts toward it (RULE CHANGE)</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>FOUNDER RULE: everything you own counts toward retirement EXCEPT your primary home and your primary car. Cash now counts (it is money you can spend), a rental counts (you can sell it), and a SECOND car counts — only the roof over your head and the car you drive are assumed off the table, because selling those is not a retirement plan. A 529 stays out (legally someone else's). The primary car = the most valuable vehicle, so a two-car household keeps the second as a real asset. Any of it is changeable per account, and the person's own choice always beats the default. This SUPERSEDES the old Term #7 default (property 0%, cash 0%, investments 100%) — five pinned tests were carrying that rule and each was updated with the reason. Knock-on, stated honestly: the expected-growth blend now includes cash, so a cash-heavy pot shows a LOWER growth rate — correct, because such a pot really does grow more slowly.</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11: "for calculating assets to count towards retirement - it should be all assets minus primary home and primary car. If they want they can change which asset should not count."</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Plan — the three questions screen (extended)</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>ONE SCREEN, EVERYTHING ON IT, SAME SCREEN EVERYWHERE. It now shows ALL three answers — never hiding one because it is already answered — prefilled with what we already hold, missing ones first, with ?focus= putting a named one at the top. "What counts toward retirement" lists every account with a tick, its value, and a tap to include or exclude it, plus the running total that will fund retirement and the three doors to add anything missing. The odds sit on the same screen and re-run as answers change, so nobody travels to find out whether it worked; the button then reads "Save &amp; go back". AND: Home, Net worth and the Plan hub now all open THIS screen from "see your real odds" — one destination, wherever it is tapped. (Home still goes to the Plan tab once real odds exist, because then there IS a full picture to see.) Sharpen your plan keeps its own separate job — how complete is the whole plan.</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Founder rules 2026-08-11: "when the screen pops up it should tell the information we already have and give them the ability to modify, and enter what's not provided. All on one screen. Once they save - come back to the NW screen" + "make sure it is the same screen which pops up every time person clicks see your real odds whether from Home, NW or Plan".</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5707,6 +5707,33 @@
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Home + Net worth — the complete state (and the hole behind it)</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>WHEN ALL THREE ANSWERS EXIST: Net worth shows the real verdict sentence ("Uncertain — retire at 65 with ~$1,607,000, lasting past 90 with ~$2,402,000 to spare ›") and tapping the card opens the Plan tab; Home shows the real gauge and percentage with "See the full picture ›", also to Plan. No sample appears beside a real verdict, and the bare "See your plan ›" appears nowhere. Verified by rendering both screens with a complete profile. THE HOLE THAT QUESTION EXPOSED: planDoor counted ANY account with a balance as "what you have", while the odds run on what is EARMARKED for retirement — so someone whose only asset is the home they live in looked COMPLETE to the door and produced no odds at all, landing on exactly the bare fallback we removed everywhere else. The gate now means what the odds mean (earmarked &gt; 0), and owning things while none of them count is reported as its own case — "choose what counts toward retirement" — which lands on the answers screen where the home can be ticked in. The door also credits what actually counts rather than every balance on file.</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Founder question 2026-08-11: "On home and NW screen - if all the information is available - what happens?"</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5734,6 +5734,33 @@
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Net worth — the verdict word carries its number</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>A BARE ADJECTIVE IS NOT A VERDICT. Net worth was the ONLY surface showing the verdict word with no number beside it — Home says "78% odds of lasting to age 90", the Plan hub says "84 in 100 paths", Net worth said just "Uncertain". The number travels with the word now: "Uncertain — 78 in 100 · retire at 65 with ~$1,607,000, lasting past 90 with ~$2,402,000 to spare ›". AND THE DEEPER CONFUSION IS ANSWERED WHERE IT IS ASKED: the info dot already on that card now defines the three words by their bands (Likely 80+, Uncertain 60-79, Unlikely under 60; retired: Holding / Watch closely / Running short) and explains why a plan can read "Uncertain" while showing money to spare — the dollar figure is the MIDDLE of the 500 runs, the odds count how many lasted at all, so "78 in 100 with $2.4m to spare" means a typical run finishes rich and 22 runs in 100 still ran out. Two true facts, not a mistake; averages hide exactly that, which is why the odds exist.</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Founder question 2026-08-11: "Uncertain — retire at 65 with ~$1,607,000, lasting past 90 with ~$2,402,000 to spare — what does uncertain mean?"</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5761,6 +5761,60 @@
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Home + Net worth + Plan — ONE wording for the odds</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>THREE SCREENS SAID ONE NUMBER THREE WAYS: Home "Uncertain — 78% odds of lasting to age 90", the Plan hub "78 in 100 paths last to 90", Net worth a bare "Uncertain". The founder's wording is now the only one: "&lt;word&gt; — xx% odds of lasting to age abc", produced by ONE helper (oddsLine) that all three screens call; the app-wide sample likewise comes from sampleOddsLine ("Sample: 84% odds of lasting to age 90"), replacing the hub's "Sample: Likely — 84 in 100 paths". A test asserts all three screens call the helpers and that no screen builds the sentence by hand or says "in 100 paths", so a fourth phrasing cannot appear.</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11: "make sure when we are using same language everywhere to convey same message. We should have the same language on home, NW and Plan for retirement — xx% odds of lasting to age abc."</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Info dot — long definitions were unreadable</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>THE INFO-DOT CARD DID NOT SCROLL. Its body was a plain Text, so anything past the bottom of the card was simply unreachable — and the retirement explanation had just grown to several screens (the method, every assumption with its number, where to change them, the honest limits, and now the meaning of the verdict words). Everything below the fold was invisible with no way to reach it. The body now scrolls inside a capped area with a visible scrollbar, and the "Got it" button stays anchored below rather than scrolling away. One shared component, so every definition in the app benefits.</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Founder finding 2026-08-11: "info dot retirement has more information than what can fit on one screen but no scrolling feature."</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5815,6 +5815,33 @@
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Performance — handoff evaluated, first tranche built</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>CLAUDE DESIGN PERFORMANCE HANDOFF received and archived (mockups/Performance-handoff-Aug-11/). Evaluated against the built screen by rendering it and dumping every visible string. ALREADY MATCHES: green header band with date, period chips each carrying their own window return or an em dash, the summary trio with its window caption, the amber missing-data banner directly below the summary, the all-accounts walk in the approved row order, the category-earnings table, and the by-class holdings list. BUILT NOW: (a) the walk is titled "· ALL ACCOUNTS", as the handoff names it — which matters because per-account walks sit directly beneath it; (b) EVERY account with value now gets its own walk. They were built only from itemised holding rows, so an account with a balance and no holdings — a CD account, anything hand-entered — vanished from the list, and the per-account walks silently stopped summing to the all-accounts walk above them. STILL OPEN, listed for the founder: category rows are not yet tappable through to a category-detail screen; the handoff's per-category "/yr" treatment for bonds and cash (their stated yield rather than a window return); the account page's "you entered this" tag with an edit affordance on user-entered records and its "See all activity (older than X)" door. NOT ADOPTED, per the founder's instruction to take UX and not calculations: the handoff's own figures and its category-return definitions — ours stay.</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-11: "Requirements for performance, and account detail screens - evaluate them and build. Again similar to NW - use these for UX design and not calculation and back end infrastructure."</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5842,6 +5842,33 @@
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Account detail — whose fact is this row?</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>EVERY ACTIVITY ROW NOW SAYS WHERE IT CAME FROM. The list mixed the broker's own records with rows the person typed and showed them identically — so a $500 deposit typed as $5,000 was indistinguishable from a Vanguard record, and equally unfixable. Your rows wear "you entered this" and a pencil; broker rows read "from Vanguard" and offer nothing, because the next sync would overwrite any change. CORRECTING a row goes through the ONE transactions engine as a reversal plus a fresh record, so the balance moves by the same tested rules as every other change rather than being patched behind the ledger's back; a row the ledger cannot reverse says so plainly and offers a correcting entry instead. Delete is on the same sheet. NOTE: the handoff's other activity item — "See all activity (older than Jul 19)" — was already built in a different form: the page shows the newest eight and offers "See all activity (N) ›". Ours truncates by count rather than by window, which after the newest-first fix is the clearer of the two.</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-11, after asking what the item meant and approving the build.</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5869,6 +5869,33 @@
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Master monitor + PRD — what is built, written down</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>THE MASTER LIST NOW CARRIES THE DAY. A new tab "Built — Aug 11" in docs/FCC-core-55-70/build-analysis-july24.xlsx records 18 built items in five groups (the Net worth Quiet-Instrument rebuild; connection honesty; the classification chain; the retirement plan; account detail + Performance), each with what was wrong, what is built, and which instruction it came from. The SUMMARY tab gains a pointer row so the day is visible from the front of the file. The 44 existing rows were left exactly as they stood — none of them is what today's work touched, and re-labelling unrelated rows would have made the monitor lie. The PRD gains an Amendments row pointing at the tab and naming the two Performance items still open by the founder's own instruction (a category-detail screen; the "/yr" stated-yield treatment, which is a calculation change).</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-11: "Update master PRD document. Go to master list of what's missing in app versus PRD, and update it listing what already build."</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-11.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5896,6 +5896,33 @@
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Plan answers — the verdict speaks the ONE app-wide wording</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>FOUND BY THE END-TO-END WALK. Home, Net worth and the Plan hub all say "&lt;word&gt; — xx% odds of lasting to age abc", but the answers screen — the very screen a person lands on to fix their odds — said "&lt;word&gt; — 0 in 100" instead, with no age in it. Worse, the same screen switched wording between its own two states: its SAMPLE line already read "Sample: 84% odds of lasting to age 90". It now calls the same shared oddsLine() helper the other three screens call, so there is one sentence in one place. Pinned by test C6, which renders all three surfaces for one person and fails unless the sentences are identical.</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11: "Let's make sure we are using same language everywhere to convey same message — xx% odds of lasting to age abc" — the walk found the one screen that was not.</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>
